--- a/data/sku_mapping.xlsx
+++ b/data/sku_mapping.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="230">
   <si>
     <t>Brand</t>
   </si>
@@ -498,6 +498,9 @@
   </si>
   <si>
     <t>HD-ASHWM230-12K</t>
+  </si>
+  <si>
+    <t>ASHWM230-24K-I</t>
   </si>
   <si>
     <t>KOW60A</t>
@@ -726,13 +729,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -743,6 +747,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -897,7 +907,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -913,6 +923,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1103,12 +1119,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1211,73 +1242,70 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1292,81 +1320,96 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <extLst>
+        <ext xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" uri="{F19249F5-4A6E-446B-B59F-E2C9F2DAA1D5}">
+          <etc:displayText val="2"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1839,36 +1882,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="7" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="14" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2500,7 +2544,7 @@
       <c r="E38">
         <v>338601543</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2">
         <v>46023</v>
       </c>
     </row>
@@ -3218,7 +3262,7 @@
         <v>343313726</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>57</v>
       </c>
@@ -3235,7 +3279,7 @@
         <v>343336423</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>57</v>
       </c>
@@ -3252,7 +3296,7 @@
         <v>343384060</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>57</v>
       </c>
@@ -3269,7 +3313,7 @@
         <v>343313669</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>57</v>
       </c>
@@ -3286,7 +3330,7 @@
         <v>343336407</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>57</v>
       </c>
@@ -3303,7 +3347,7 @@
         <v>343336441</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -3320,7 +3364,7 @@
         <v>337053191</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -3337,7 +3381,7 @@
         <v>337053212</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -3354,7 +3398,7 @@
         <v>339721314</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -3371,7 +3415,7 @@
         <v>339721345</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -3388,7 +3432,7 @@
         <v>338699799</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3405,7 +3449,7 @@
         <v>338698352</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -3421,8 +3465,11 @@
       <c r="E92">
         <v>341731268</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="G92" s="2">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="93" ht="15" spans="1:7">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -3430,55 +3477,58 @@
         <v>155</v>
       </c>
       <c r="C93" t="s">
+        <v>148</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E93">
+        <v>341731268</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" t="s">
         <v>156</v>
       </c>
-      <c r="D93" t="s">
+      <c r="C94" t="s">
         <v>157</v>
-      </c>
-      <c r="E93">
-        <v>337553514</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
-        <v>39</v>
-      </c>
-      <c r="B94" t="s">
-        <v>155</v>
-      </c>
-      <c r="C94" t="s">
-        <v>156</v>
       </c>
       <c r="D94" t="s">
         <v>158</v>
       </c>
       <c r="E94">
-        <v>341706943</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>337553514</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="D95" t="s">
         <v>159</v>
       </c>
       <c r="E95">
-        <v>332510548</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>341706943</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C96" t="s">
         <v>34</v>
@@ -3487,7 +3537,7 @@
         <v>160</v>
       </c>
       <c r="E96">
-        <v>336709158</v>
+        <v>332510548</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3495,16 +3545,16 @@
         <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="C97" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
         <v>161</v>
       </c>
       <c r="E97">
-        <v>344399102</v>
+        <v>336709158</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3512,7 +3562,7 @@
         <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
@@ -3521,13 +3571,7 @@
         <v>162</v>
       </c>
       <c r="E98">
-        <v>338601543</v>
-      </c>
-      <c r="F98">
-        <v>46240</v>
-      </c>
-      <c r="G98">
-        <v>46258</v>
+        <v>344399102</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3546,673 +3590,696 @@
       <c r="E99">
         <v>338601543</v>
       </c>
-      <c r="F99">
-        <v>46023</v>
-      </c>
-      <c r="G99">
-        <v>46239</v>
+      <c r="F99" s="2">
+        <v>46240</v>
+      </c>
+      <c r="G99" s="2">
+        <v>46258</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" t="s">
         <v>164</v>
       </c>
-      <c r="B100" t="s">
-        <v>165</v>
-      </c>
-      <c r="C100" t="s">
-        <v>166</v>
-      </c>
-      <c r="D100" t="s">
-        <v>167</v>
-      </c>
       <c r="E100">
-        <v>322614014</v>
+        <v>338601543</v>
+      </c>
+      <c r="F100" s="2">
+        <v>46023</v>
+      </c>
+      <c r="G100" s="2">
+        <v>46239</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B101" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" t="s">
         <v>168</v>
       </c>
-      <c r="C101" t="s">
-        <v>166</v>
-      </c>
-      <c r="D101" t="s">
-        <v>169</v>
-      </c>
       <c r="E101">
-        <v>335893572</v>
+        <v>322614014</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B102" t="s">
+        <v>169</v>
+      </c>
+      <c r="C102" t="s">
+        <v>167</v>
+      </c>
+      <c r="D102" t="s">
         <v>170</v>
       </c>
-      <c r="C102" t="s">
-        <v>166</v>
-      </c>
-      <c r="D102" t="s">
-        <v>171</v>
-      </c>
       <c r="E102">
-        <v>335893574</v>
+        <v>335893572</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B103" t="s">
+        <v>171</v>
+      </c>
+      <c r="C103" t="s">
+        <v>167</v>
+      </c>
+      <c r="D103" t="s">
         <v>172</v>
       </c>
-      <c r="C103" t="s">
-        <v>166</v>
-      </c>
-      <c r="D103" t="s">
-        <v>173</v>
-      </c>
       <c r="E103">
-        <v>335893575</v>
+        <v>335893574</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B104" t="s">
+        <v>173</v>
+      </c>
+      <c r="C104" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" t="s">
         <v>174</v>
       </c>
-      <c r="C104" t="s">
-        <v>166</v>
-      </c>
-      <c r="D104" t="s">
-        <v>175</v>
-      </c>
       <c r="E104">
-        <v>335893576</v>
+        <v>335893575</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B105" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C105" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D105" t="s">
         <v>176</v>
       </c>
       <c r="E105">
-        <v>338997256</v>
+        <v>335893576</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B106" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D106" t="s">
         <v>177</v>
       </c>
       <c r="E106">
-        <v>322754489</v>
+        <v>338997256</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B107" t="s">
+        <v>171</v>
+      </c>
+      <c r="C107" t="s">
+        <v>167</v>
+      </c>
+      <c r="D107" t="s">
         <v>178</v>
       </c>
-      <c r="C107" t="s">
-        <v>166</v>
-      </c>
-      <c r="D107" t="s">
-        <v>179</v>
-      </c>
       <c r="E107">
-        <v>336299081</v>
+        <v>322754489</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B108" t="s">
+        <v>179</v>
+      </c>
+      <c r="C108" t="s">
+        <v>167</v>
+      </c>
+      <c r="D108" t="s">
         <v>180</v>
       </c>
-      <c r="C108" t="s">
-        <v>166</v>
-      </c>
-      <c r="D108" t="s">
-        <v>181</v>
-      </c>
       <c r="E108">
-        <v>336299082</v>
+        <v>336299081</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B109" t="s">
+        <v>181</v>
+      </c>
+      <c r="C109" t="s">
+        <v>167</v>
+      </c>
+      <c r="D109" t="s">
         <v>182</v>
       </c>
-      <c r="C109" t="s">
-        <v>166</v>
-      </c>
-      <c r="D109" t="s">
-        <v>183</v>
-      </c>
       <c r="E109">
-        <v>322428819</v>
+        <v>336299082</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B110" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C110" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D110" t="s">
         <v>184</v>
       </c>
       <c r="E110">
-        <v>331384752</v>
+        <v>322428819</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C111" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D111" t="s">
         <v>185</v>
       </c>
       <c r="E111">
-        <v>336299064</v>
+        <v>331384752</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B112" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D112" t="s">
         <v>186</v>
       </c>
       <c r="E112">
-        <v>336299065</v>
+        <v>336299064</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C113" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D113" t="s">
         <v>187</v>
       </c>
       <c r="E113">
-        <v>322540898</v>
+        <v>336299065</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B114" t="s">
+        <v>171</v>
+      </c>
+      <c r="C114" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" t="s">
         <v>188</v>
       </c>
-      <c r="C114" t="s">
-        <v>166</v>
-      </c>
-      <c r="D114" t="s">
-        <v>189</v>
-      </c>
       <c r="E114">
-        <v>331384746</v>
+        <v>322540898</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B115" t="s">
+        <v>189</v>
+      </c>
+      <c r="C115" t="s">
+        <v>167</v>
+      </c>
+      <c r="D115" t="s">
         <v>190</v>
       </c>
-      <c r="C115" t="s">
-        <v>166</v>
-      </c>
-      <c r="D115" t="s">
-        <v>191</v>
-      </c>
       <c r="E115">
-        <v>331385417</v>
+        <v>331384746</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
+        <v>165</v>
+      </c>
+      <c r="B116" t="s">
+        <v>191</v>
+      </c>
+      <c r="C116" t="s">
+        <v>167</v>
+      </c>
+      <c r="D116" t="s">
         <v>192</v>
       </c>
-      <c r="B116" t="s">
-        <v>193</v>
-      </c>
-      <c r="C116" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" t="s">
-        <v>194</v>
-      </c>
       <c r="E116">
-        <v>322733681</v>
+        <v>331385417</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B117" t="s">
+        <v>194</v>
+      </c>
+      <c r="C117" t="s">
+        <v>167</v>
+      </c>
+      <c r="D117" t="s">
         <v>195</v>
       </c>
-      <c r="C117" t="s">
-        <v>166</v>
-      </c>
-      <c r="D117" t="s">
-        <v>196</v>
-      </c>
       <c r="E117">
-        <v>331385429</v>
+        <v>322733681</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B118" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C118" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D118" t="s">
         <v>197</v>
       </c>
       <c r="E118">
-        <v>329471073</v>
+        <v>331385429</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C119" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D119" t="s">
         <v>198</v>
       </c>
       <c r="E119">
-        <v>329471100</v>
+        <v>329471073</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="B120" t="s">
+        <v>173</v>
+      </c>
+      <c r="C120" t="s">
+        <v>167</v>
+      </c>
+      <c r="D120" t="s">
         <v>199</v>
       </c>
-      <c r="C120" t="s">
-        <v>166</v>
-      </c>
-      <c r="D120" t="s">
-        <v>200</v>
-      </c>
       <c r="E120">
-        <v>325174476</v>
+        <v>329471100</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B121" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C121" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D121" t="s">
         <v>201</v>
       </c>
       <c r="E121">
-        <v>325187166</v>
+        <v>325174476</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B122" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C122" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D122" t="s">
         <v>202</v>
       </c>
       <c r="E122">
-        <v>329471054</v>
+        <v>325187166</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="C123" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D123" t="s">
         <v>203</v>
       </c>
       <c r="E123">
-        <v>331385430</v>
+        <v>329471054</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D124" t="s">
         <v>204</v>
       </c>
       <c r="E124">
-        <v>331385431</v>
+        <v>331385430</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C125" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D125" t="s">
         <v>205</v>
       </c>
       <c r="E125">
-        <v>322932522</v>
+        <v>331385431</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B126" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C126" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D126" t="s">
         <v>206</v>
       </c>
       <c r="E126">
-        <v>331385425</v>
+        <v>322932522</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B127" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C127" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D127" t="s">
         <v>207</v>
       </c>
       <c r="E127">
-        <v>325148676</v>
+        <v>331385425</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B128" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C128" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D128" t="s">
         <v>208</v>
       </c>
       <c r="E128">
-        <v>322484420</v>
+        <v>325148676</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B129" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C129" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D129" t="s">
         <v>209</v>
       </c>
       <c r="E129">
-        <v>322733599</v>
+        <v>322484420</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C130" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D130" t="s">
         <v>210</v>
       </c>
       <c r="E130">
-        <v>336299061</v>
+        <v>322733599</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B131" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C131" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D131" t="s">
         <v>211</v>
       </c>
       <c r="E131">
-        <v>325158743</v>
+        <v>336299061</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B132" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C132" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D132" t="s">
         <v>212</v>
       </c>
       <c r="E132">
-        <v>322811050</v>
+        <v>325158743</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B133" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C133" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D133" t="s">
         <v>213</v>
       </c>
       <c r="E133">
-        <v>334249602</v>
+        <v>322811050</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B134" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D134" t="s">
         <v>214</v>
       </c>
       <c r="E134">
-        <v>334249603</v>
+        <v>334249602</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="B135" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C135" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D135" t="s">
         <v>215</v>
       </c>
       <c r="E135">
-        <v>338997279</v>
+        <v>334249603</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C136" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D136" t="s">
         <v>216</v>
       </c>
       <c r="E136">
-        <v>338997424</v>
+        <v>338997279</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B137" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C137" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D137" t="s">
         <v>217</v>
       </c>
       <c r="E137">
-        <v>336299059</v>
+        <v>338997424</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B138" t="s">
+        <v>175</v>
+      </c>
+      <c r="C138" t="s">
+        <v>167</v>
+      </c>
+      <c r="D138" t="s">
         <v>218</v>
       </c>
-      <c r="C138" t="s">
-        <v>166</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="E138">
+        <v>336299059</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>165</v>
+      </c>
+      <c r="B139" t="s">
         <v>219</v>
       </c>
-      <c r="E138">
+      <c r="C139" t="s">
+        <v>167</v>
+      </c>
+      <c r="D139" t="s">
+        <v>220</v>
+      </c>
+      <c r="E139">
         <v>325187106</v>
       </c>
     </row>
@@ -4236,58 +4303,58 @@
   <sheetData>
     <row r="1" ht="15" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
         <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
